--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI21"/>
+  <dimension ref="A1:BI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,27 +1142,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46149.54166666666</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="5">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46149.54166666666</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="6">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46149.58333333334</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="7">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46149.58333333334</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="8">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46149.58333333334</v>
+        <v>46149.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46149.625</v>
+        <v>46149.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="14">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,6 +4679,794 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Miami FC II</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Etoile du Sahel</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CA Bizertin</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Marsa</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CS Sfaxien</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
         <v>46149.875</v>
       </c>
     </row>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI25"/>
+  <dimension ref="A1:BI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46149.58333333334</v>
+        <v>46149.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.70833333334</v>
       </c>
     </row>
     <row r="17">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,6 +5467,597 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Miami FC II</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3" t="n">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Austria 2. Liga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Floridsdorfer AC</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SV Stripfing Weiden</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3" t="n">
         <v>46149.875</v>
       </c>
     </row>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -268,16 +268,19 @@
     <t>Dubočica</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Dinamo Jug</t>
+    <t>Dinamo Tbilisi</t>
   </si>
   <si>
     <t>Difaâ El Jadida</t>
@@ -286,18 +289,15 @@
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
@@ -307,58 +307,61 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
     <t>Kairouan</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
+    <t>Spaeri</t>
   </si>
   <si>
     <t>Hassania Agadir</t>
@@ -367,18 +370,15 @@
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Spaeri</t>
+    <t>Masr</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Masr</t>
-  </si>
-  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
@@ -388,40 +388,40 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
     <t>Monastir</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
     <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1539,10 +1539,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -1724,10 +1724,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -2097,7 +2097,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -2318,133 +2318,133 @@
         <v>136</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -2503,133 +2503,133 @@
         <v>136</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -3019,10 +3019,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>93</v>
@@ -3204,7 +3204,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3574,7 +3574,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3944,7 +3944,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>80</v>
@@ -4314,7 +4314,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4684,10 +4684,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
         <v>102</v>
@@ -5054,7 +5054,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5424,10 +5424,10 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
         <v>106</v>
@@ -5609,10 +5609,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
         <v>107</v>
@@ -5794,10 +5794,10 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
         <v>108</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -232,30 +232,30 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -265,6 +265,9 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
@@ -277,18 +280,15 @@
     <t>Tukums</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
@@ -307,45 +307,48 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Olympique Béja</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
   </si>
   <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
@@ -358,18 +361,15 @@
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
     <t>Spaeri</t>
   </si>
   <si>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
@@ -388,40 +388,40 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
   </si>
   <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
     <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1724,10 +1724,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -1909,10 +1909,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>87</v>
@@ -2318,133 +2318,133 @@
         <v>136</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2503,133 +2503,133 @@
         <v>136</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3574,7 +3574,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3944,10 +3944,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>98</v>
@@ -4129,7 +4129,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
@@ -4314,7 +4314,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4684,10 +4684,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>102</v>
@@ -5054,7 +5054,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5424,7 +5424,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>81</v>
@@ -5609,7 +5609,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="138">
   <si>
     <t>Date</t>
   </si>
@@ -229,15 +229,15 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
@@ -247,15 +247,15 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -268,42 +268,42 @@
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tukums</t>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
+    <t>Auda</t>
+  </si>
+  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
@@ -313,78 +313,78 @@
     <t>Birmingham Legion</t>
   </si>
   <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>ES Tunis</t>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
   </si>
   <si>
     <t>Olympique Béja</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Spaeri</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
@@ -394,37 +394,40 @@
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
-    <t>Club Africain</t>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
   </si>
   <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
     <t>incomplete</t>
+  </si>
+  <si>
+    <t>canceled</t>
   </si>
 </sst>
 </file>
@@ -1724,10 +1727,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -1909,10 +1912,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>87</v>
@@ -2097,7 +2100,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -2133,133 +2136,133 @@
         <v>136</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2318,133 +2321,133 @@
         <v>136</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2467,7 +2470,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -2834,10 +2837,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>92</v>
@@ -3019,10 +3022,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>93</v>
@@ -3204,7 +3207,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3389,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -3574,7 +3577,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -4869,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -4905,7 +4908,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5424,7 +5427,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>81</v>
@@ -5609,7 +5612,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -232,30 +232,30 @@
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>Russia FNL</t>
   </si>
   <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -274,75 +274,75 @@
     <t>Borac Čačak</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Tukums</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
+    <t>Auda</t>
   </si>
   <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
-    <t>Auda</t>
-  </si>
-  <si>
-    <t>National Bank of Egypt</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Marsa</t>
   </si>
   <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
@@ -355,73 +355,73 @@
     <t>Grafičar</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>FAP</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Spaeri</t>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
+    <t>Grobiņa</t>
   </si>
   <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
-    <t>Ismaily SC</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
-    <t>Miami FC II</t>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
   </si>
   <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
     <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1727,10 +1727,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -1912,10 +1912,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>87</v>
@@ -2285,7 +2285,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>89</v>
@@ -2470,7 +2470,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -3207,7 +3207,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3392,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -3577,7 +3577,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3765,7 +3765,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>97</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
         <v>80</v>
@@ -4687,7 +4687,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -4872,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -4908,7 +4908,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5242,7 +5242,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
         <v>80</v>
@@ -5430,7 +5430,7 @@
         <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
         <v>106</v>
@@ -5463,7 +5463,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5612,7 +5612,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>
@@ -5797,7 +5797,7 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -241,21 +241,21 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -268,15 +268,15 @@
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
     <t>Tukums</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>Difaâ El Jadida</t>
   </si>
   <si>
+    <t>Auda</t>
+  </si>
+  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
@@ -307,57 +307,57 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Marsa</t>
+    <t>Zarzis</t>
   </si>
   <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>FAP</t>
-  </si>
-  <si>
     <t>Ogre United</t>
   </si>
   <si>
@@ -370,12 +370,12 @@
     <t>Hassania Agadir</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
@@ -388,40 +388,40 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>Miami FC II</t>
   </si>
   <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
+    <t>Métlaoui</t>
   </si>
   <si>
     <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2652,10 +2652,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -2837,10 +2837,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>92</v>
@@ -3765,7 +3765,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>97</v>
@@ -3947,10 +3947,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>98</v>
@@ -4132,7 +4132,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,10 +4502,10 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>101</v>
@@ -4723,7 +4723,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -5057,7 +5057,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5242,7 +5242,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>80</v>
@@ -5427,10 +5427,10 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
         <v>106</v>
@@ -5463,7 +5463,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5612,7 +5612,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>
@@ -5797,7 +5797,7 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -244,18 +244,18 @@
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -265,21 +265,21 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
@@ -289,78 +289,78 @@
     <t>Difaâ El Jadida</t>
   </si>
   <si>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
-    <t>Haras El Hodood</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>Olympique Béja</t>
+    <t>Huntsville City</t>
   </si>
   <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>FAP</t>
-  </si>
-  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
@@ -370,58 +370,58 @@
     <t>Hassania Agadir</t>
   </si>
   <si>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
+    <t>Masr</t>
+  </si>
+  <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Masr</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
     <t>Club Africain</t>
   </si>
   <si>
-    <t>Jeunesse Sportive Omrane</t>
+    <t>Carolina Core</t>
   </si>
   <si>
     <t>CA Bizertin</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
   </si>
   <si>
     <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1542,10 +1542,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -1912,10 +1912,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>87</v>
@@ -2652,10 +2652,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -3022,10 +3022,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>93</v>
@@ -3207,7 +3207,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3392,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -4132,7 +4132,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
@@ -4168,7 +4168,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,10 +4502,10 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>101</v>
@@ -4687,7 +4687,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -4723,7 +4723,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5242,10 +5242,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
         <v>105</v>
@@ -5427,10 +5427,10 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
         <v>106</v>
@@ -5612,10 +5612,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
         <v>107</v>
@@ -5797,7 +5797,7 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -265,39 +265,39 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
     <t>Tukums</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
+    <t>Dinamo Tbilisi</t>
   </si>
   <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
+    <t>Auda</t>
+  </si>
+  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
-    <t>Auda</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -307,78 +307,78 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>AS Slimane</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>FAP</t>
-  </si>
-  <si>
     <t>Ogre United</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
+    <t>Spaeri</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Ismaily SC</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
     <t>Al Nassr</t>
   </si>
   <si>
@@ -388,40 +388,40 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>Gabès</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2100,7 +2100,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -2136,133 +2136,133 @@
         <v>136</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>89</v>
@@ -2321,133 +2321,133 @@
         <v>136</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>92</v>
@@ -3022,10 +3022,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>93</v>
@@ -3798,7 +3798,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>80</v>
@@ -4132,10 +4132,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>99</v>
@@ -4168,7 +4168,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>80</v>
@@ -4687,10 +4687,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
         <v>102</v>
@@ -4872,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -5057,7 +5057,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5242,10 +5242,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
         <v>105</v>
@@ -5427,7 +5427,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>80</v>
@@ -5612,10 +5612,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
         <v>107</v>
@@ -5797,7 +5797,7 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -223,36 +223,36 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -265,36 +265,36 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Tekstilac Odžaci</t>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
+    <t>Auda</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
@@ -307,75 +307,75 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Spaeri</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
+    <t>Grobiņa</t>
   </si>
   <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
@@ -388,40 +388,40 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Gabès</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1175,7 +1175,7 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
@@ -1357,7 +1357,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
         <v>80</v>
@@ -1545,7 +1545,7 @@
         <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -1727,7 +1727,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
         <v>80</v>
@@ -1912,7 +1912,7 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>80</v>
@@ -2100,7 +2100,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -2136,133 +2136,133 @@
         <v>136</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2321,133 +2321,133 @@
         <v>136</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2470,7 +2470,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -2652,10 +2652,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -2837,10 +2837,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>92</v>
@@ -3392,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -3577,7 +3577,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3798,7 +3798,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4132,10 +4132,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>99</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
         <v>80</v>
@@ -4687,10 +4687,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>102</v>
@@ -4872,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -5057,10 +5057,10 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>104</v>
@@ -5242,7 +5242,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>80</v>
@@ -5427,7 +5427,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>80</v>
@@ -5612,7 +5612,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>
@@ -5648,7 +5648,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5797,10 +5797,10 @@
         <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
         <v>108</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -223,33 +223,33 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
@@ -265,78 +265,78 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Tukums</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
+    <t>Haras El Hodood</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
-    <t>Haras El Hodood</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
@@ -346,76 +346,76 @@
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>FAP</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Spaeri</t>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
+    <t>Masr</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Masr</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
     <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
   </si>
   <si>
     <t>SV Stripfing Weiden</t>
@@ -1175,7 +1175,7 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
@@ -1357,7 +1357,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
         <v>80</v>
@@ -1542,7 +1542,7 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
         <v>80</v>
@@ -1727,7 +1727,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
         <v>80</v>
@@ -1915,7 +1915,7 @@
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>87</v>
@@ -2285,7 +2285,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>89</v>
@@ -2470,7 +2470,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -2652,10 +2652,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -3022,10 +3022,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>93</v>
@@ -3207,7 +3207,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3392,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -3577,7 +3577,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3947,7 +3947,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>80</v>
@@ -5057,10 +5057,10 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
         <v>104</v>
@@ -5242,10 +5242,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
         <v>105</v>
@@ -5427,7 +5427,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
         <v>80</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,33 +229,33 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -265,163 +265,163 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Tukums</t>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
+    <t>Auda</t>
+  </si>
+  <si>
+    <t>Haras El Hodood</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
-    <t>Auda</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>FAP</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
+    <t>Grobiņa</t>
+  </si>
+  <si>
+    <t>Masr</t>
   </si>
   <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
-    <t>Grobiņa</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
     <t>Métlaoui</t>
   </si>
   <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
     <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1727,10 +1727,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -1912,10 +1912,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>87</v>
@@ -2100,7 +2100,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -2136,133 +2136,133 @@
         <v>136</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>89</v>
@@ -2506,133 +2506,133 @@
         <v>136</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2652,10 +2652,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -3022,10 +3022,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>93</v>
@@ -3207,7 +3207,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3392,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -3577,7 +3577,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3765,7 +3765,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>97</v>
@@ -3947,10 +3947,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>98</v>
@@ -4132,7 +4132,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>80</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>80</v>
@@ -4687,7 +4687,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -4872,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -5057,7 +5057,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5242,10 +5242,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
         <v>105</v>
@@ -5427,7 +5427,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>80</v>
@@ -5648,7 +5648,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5800,7 +5800,7 @@
         <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
         <v>108</v>
@@ -5833,7 +5833,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P28">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,33 +229,33 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -268,160 +268,160 @@
     <t>Dubočica</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Tekstilac Odžaci</t>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
     <t>Auda</t>
   </si>
   <si>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Chayka</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>Spaeri</t>
   </si>
   <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
     <t>Grobiņa</t>
   </si>
   <si>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1542,10 +1542,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -1727,10 +1727,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -2100,7 +2100,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
@@ -2321,133 +2321,133 @@
         <v>136</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2470,7 +2470,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -2506,133 +2506,133 @@
         <v>136</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>80</v>
@@ -3392,7 +3392,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -3577,7 +3577,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>80</v>
@@ -3765,7 +3765,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>97</v>
@@ -3798,7 +3798,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>98</v>
@@ -4135,7 +4135,7 @@
         <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>99</v>
@@ -4317,7 +4317,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
         <v>80</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>80</v>
@@ -4687,7 +4687,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -4872,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>80</v>
@@ -5057,7 +5057,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>80</v>
@@ -5242,7 +5242,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>80</v>
@@ -5612,7 +5612,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
         <v>80</v>
@@ -5800,7 +5800,7 @@
         <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
         <v>108</v>
@@ -5833,7 +5833,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P28">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="135">
   <si>
     <t>Date</t>
   </si>
@@ -241,21 +241,18 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -265,21 +262,21 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
+    <t>Borac Čačak</t>
   </si>
   <si>
     <t>Tukums</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
@@ -292,12 +289,12 @@
     <t>Auda</t>
   </si>
   <si>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
@@ -307,60 +304,57 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>Marsa</t>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
   </si>
   <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Chayka</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
+    <t>Grafičar</t>
   </si>
   <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
@@ -373,12 +367,12 @@
     <t>Grobiņa</t>
   </si>
   <si>
+    <t>Masr</t>
+  </si>
+  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
@@ -388,40 +382,37 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>CS Sfaxien</t>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Gabès</t>
   </si>
   <si>
     <t>Miami FC II</t>
   </si>
   <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
     <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -791,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI28"/>
+  <dimension ref="A1:BI27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -990,13 +981,13 @@
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1023,7 +1014,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1175,13 +1166,13 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1208,7 +1199,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1360,13 +1351,13 @@
         <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1393,7 +1384,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1542,16 +1533,16 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1578,7 +1569,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1730,13 +1721,13 @@
         <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1763,7 +1754,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1912,16 +1903,16 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1948,7 +1939,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2100,13 +2091,13 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2133,7 +2124,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2285,13 +2276,13 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2318,7 +2309,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P9">
         <v>1.75</v>
@@ -2470,13 +2461,13 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2503,7 +2494,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2655,13 +2646,13 @@
         <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2688,7 +2679,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2840,13 +2831,13 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2873,7 +2864,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3025,13 +3016,13 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3058,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3210,13 +3201,13 @@
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3243,7 +3234,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3395,13 +3386,13 @@
         <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3428,7 +3419,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3580,13 +3571,13 @@
         <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3613,7 +3604,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3765,13 +3756,13 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3798,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3953,10 +3944,10 @@
         <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3983,7 +3974,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4132,16 +4123,16 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4168,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4317,16 +4308,16 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4353,7 +4344,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4502,16 +4493,16 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4538,7 +4529,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4687,16 +4678,16 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4723,7 +4714,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4872,16 +4863,16 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4908,7 +4899,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5057,16 +5048,16 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5093,7 +5084,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5242,16 +5233,16 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5278,7 +5269,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5433,10 +5424,10 @@
         <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5463,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5612,16 +5603,16 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5648,7 +5639,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5786,191 +5777,6 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="28" spans="1:61">
-      <c r="A28" s="2">
-        <v>46149</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" t="s">
-        <v>135</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>-1</v>
-      </c>
-      <c r="N28">
-        <v>-1</v>
-      </c>
-      <c r="O28" t="s">
-        <v>136</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AO28">
-        <v>0</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>0</v>
-      </c>
-      <c r="BC28">
-        <v>0</v>
-      </c>
-      <c r="BD28">
-        <v>0</v>
-      </c>
-      <c r="BE28">
-        <v>0</v>
-      </c>
-      <c r="BF28">
-        <v>0</v>
-      </c>
-      <c r="BG28">
-        <v>0</v>
-      </c>
-      <c r="BH28">
-        <v>0</v>
-      </c>
-      <c r="BI28" s="3">
         <v>46149.875</v>
       </c>
     </row>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,27 +229,27 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -262,157 +262,157 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
+    <t>Tukums</t>
   </si>
   <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tukums</t>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Dinamo Tbilisi</t>
+    <t>Haras El Hodood</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
+    <t>Al Shabab</t>
+  </si>
+  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Olympique Béja</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
     <t>Kairouan</t>
   </si>
   <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
+    <t>Ogre United</t>
   </si>
   <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
-    <t>Spaeri</t>
+    <t>Masr</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
+    <t>Al Nassr</t>
+  </si>
+  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
     <t>CS Sfaxien</t>
   </si>
   <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
     <t>Monastir</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -1903,10 +1903,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2461,7 +2461,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3938,10 +3938,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4344,7 +4344,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>79</v>
@@ -4899,7 +4899,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5048,10 +5048,10 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
         <v>103</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -5418,10 +5418,10 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
         <v>105</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,6 +262,12 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Borac Čačak</t>
   </si>
   <si>
@@ -271,30 +277,24 @@
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
@@ -304,42 +304,48 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
     <t>Zarzis</t>
   </si>
   <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
     <t>Olympique Béja</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
@@ -349,30 +355,24 @@
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>FAP</t>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>Spaeri</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
     <t>Masr</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
     <t>Al Nassr</t>
   </si>
   <si>
@@ -382,37 +382,37 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
     <t>Métlaoui</t>
   </si>
   <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
     <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Monastir</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1348,10 +1348,10 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2312,133 +2312,133 @@
         <v>133</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3756,7 +3756,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>96</v>
@@ -3938,7 +3938,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4493,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -4678,7 +4678,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>79</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -4899,7 +4899,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5048,10 +5048,10 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
         <v>103</v>
@@ -5236,7 +5236,7 @@
         <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -5269,7 +5269,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5603,7 +5603,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -265,6 +265,9 @@
     <t>Dubočica</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Tukums</t>
   </si>
   <si>
@@ -274,75 +277,75 @@
     <t>Dinamo Jug</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
+    <t>Auda</t>
+  </si>
+  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
-    <t>Auda</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
-    <t>AS Slimane</t>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Marsa</t>
   </si>
   <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>Marsa</t>
+    <t>Olympique Béja</t>
   </si>
   <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
@@ -352,67 +355,64 @@
     <t>Stepojevac Vaga</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Grobiņa</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>Gabès</t>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
   </si>
   <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
-    <t>CS Sfaxien</t>
+    <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1348,10 +1348,10 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -5233,7 +5233,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>79</v>
@@ -5269,7 +5269,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P25">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,6 +262,9 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
@@ -271,75 +274,75 @@
     <t>Tukums</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
+    <t>Auda</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
+    <t>Al Shabab</t>
+  </si>
+  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
@@ -349,70 +352,67 @@
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
     <t>Spaeri</t>
   </si>
   <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Pogoń Grod. Mazowiecki</t>
+    <t>Grobiņa</t>
   </si>
   <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
+    <t>Al Nassr</t>
+  </si>
+  <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
     <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3756,7 +3756,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>96</v>
@@ -3938,7 +3938,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4493,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4866,7 +4866,7 @@
         <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -5048,7 +5048,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,15 +229,15 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
@@ -265,52 +265,61 @@
     <t>Borac Čačak</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Dinamo Jug</t>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
   </si>
   <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>Dinamo Tbilisi</t>
+    <t>National Bank of Egypt</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
     <t>Kairouan</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Marsa</t>
+    <t>Birmingham Legion</t>
   </si>
   <si>
     <t>Olympique Béja</t>
@@ -322,73 +331,73 @@
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>AS Slimane</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>Grafičar</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Spaeri</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Spaeri</t>
+    <t>Ismaily SC</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
+    <t>UTS Rabat</t>
+  </si>
+  <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
     <t>Monastir</t>
   </si>
   <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
+    <t>Miami FC II</t>
   </si>
   <si>
     <t>Jeunesse Sportive Omrane</t>
@@ -400,19 +409,10 @@
     <t>Ben Guerdane</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
     <t>Gabès</t>
   </si>
   <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
     <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2461,7 +2461,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -2867,13 +2867,13 @@
         <v>133</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3938,10 +3938,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4717,13 +4717,13 @@
         <v>133</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -5639,7 +5639,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,28 +262,31 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
     <t>Tukums</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
+    <t>Haras El Hodood</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
@@ -292,76 +295,76 @@
     <t>Auda</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
-    <t>FAP</t>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Pogoń Grod. Mazowiecki</t>
+    <t>Masr</t>
   </si>
   <si>
     <t>Ismaily SC</t>
@@ -370,49 +373,46 @@
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Masr</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
     <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1903,10 +1903,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2312,133 +2312,133 @@
         <v>133</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -2867,13 +2867,13 @@
         <v>133</v>
       </c>
       <c r="P12">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,13 +3052,13 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3938,10 +3938,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>99</v>
@@ -4347,13 +4347,13 @@
         <v>133</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>80</v>
@@ -4717,13 +4717,13 @@
         <v>133</v>
       </c>
       <c r="P22">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -5639,7 +5639,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
+    <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,19 +262,22 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tukums</t>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
@@ -283,7 +286,7 @@
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
+    <t>Auda</t>
   </si>
   <si>
     <t>Haras El Hodood</t>
@@ -292,67 +295,67 @@
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Spaeri</t>
@@ -361,7 +364,7 @@
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Hassania Agadir</t>
+    <t>Grobiņa</t>
   </si>
   <si>
     <t>Masr</t>
@@ -370,49 +373,46 @@
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1348,10 +1348,10 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -1903,10 +1903,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2312,133 +2312,133 @@
         <v>133</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,13 +3052,13 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3789,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -4123,10 +4123,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>98</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
         <v>99</v>
@@ -4347,13 +4347,13 @@
         <v>133</v>
       </c>
       <c r="P20">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -4902,13 +4902,13 @@
         <v>133</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
@@ -5233,7 +5233,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>79</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5603,7 +5603,7 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,27 +229,27 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -265,154 +265,154 @@
     <t>Dinamo Jug</t>
   </si>
   <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
     <t>Tukums</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
     <t>Dubočica</t>
   </si>
   <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>ŁKS Łódź</t>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
-    <t>National Bank of Egypt</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
+    <t>Olympique Béja</t>
   </si>
   <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Pogoń Grod. Mazowiecki</t>
+    <t>Masr</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
-    <t>Ismaily SC</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
     <t>Club Africain</t>
   </si>
   <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
+    <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1348,10 +1348,10 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,13 +3052,13 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3756,7 +3756,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>96</v>
@@ -3789,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4123,10 +4123,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>98</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -4902,13 +4902,13 @@
         <v>133</v>
       </c>
       <c r="P23">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
@@ -5084,7 +5084,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5603,10 +5603,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
         <v>106</v>
@@ -5642,13 +5642,13 @@
         <v>133</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,6 +262,9 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
@@ -271,19 +274,19 @@
     <t>Tukums</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
     <t>Dubočica</t>
   </si>
   <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
+    <t>Auda</t>
   </si>
   <si>
     <t>Haras El Hodood</t>
@@ -292,54 +295,54 @@
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
+    <t>Marsa</t>
   </si>
   <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Olympique Béja</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
@@ -349,19 +352,19 @@
     <t>Ogre United</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
+    <t>Grobiņa</t>
   </si>
   <si>
     <t>Masr</t>
@@ -370,49 +373,46 @@
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
+    <t>CS Sfaxien</t>
   </si>
   <si>
     <t>Métlaoui</t>
   </si>
   <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
     <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,13 +3052,13 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3792,13 +3792,13 @@
         <v>133</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -5048,7 +5048,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
@@ -5084,7 +5084,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5603,10 +5603,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
         <v>106</v>
@@ -5642,13 +5642,13 @@
         <v>133</v>
       </c>
       <c r="P27">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -223,10 +223,13 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
@@ -235,24 +238,21 @@
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,19 +262,22 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
@@ -283,76 +286,76 @@
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
-    <t>National Bank of Egypt</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>FAP</t>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>Spaeri</t>
@@ -361,58 +364,55 @@
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
+    <t>Masr</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
-    <t>Ismaily SC</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
     <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1166,7 +1166,7 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>82</v>
@@ -1348,7 +1348,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
         <v>79</v>
@@ -1533,7 +1533,7 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
         <v>79</v>
@@ -1721,7 +1721,7 @@
         <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -1903,7 +1903,7 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>79</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,13 +3052,13 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3756,7 +3756,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>96</v>
@@ -3792,13 +3792,13 @@
         <v>133</v>
       </c>
       <c r="P17">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4493,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -4678,7 +4678,7 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
         <v>79</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -4899,7 +4899,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5603,10 +5603,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
         <v>106</v>
@@ -5642,13 +5642,13 @@
         <v>133</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -223,33 +223,33 @@
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -262,157 +262,157 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Tukums</t>
   </si>
   <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
-    <t>Difaâ El Jadida</t>
+    <t>Auda</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
   </si>
   <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
-    <t>Auda</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Kairouan</t>
   </si>
   <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
     <t>AS Slimane</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>FAP</t>
-  </si>
-  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
+    <t>Grobiņa</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
   </si>
   <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Grobiņa</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>Monastir</t>
   </si>
   <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
     <t>Gabès</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1166,7 +1166,7 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>82</v>
@@ -1348,7 +1348,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
         <v>79</v>
@@ -1536,7 +1536,7 @@
         <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1572,13 +1572,13 @@
         <v>133</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
         <v>79</v>
@@ -1903,7 +1903,7 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
         <v>79</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,13 +3052,13 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3938,10 +3938,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4344,7 +4344,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -4899,16 +4899,16 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>
@@ -5603,10 +5603,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
         <v>106</v>
@@ -5642,13 +5642,13 @@
         <v>133</v>
       </c>
       <c r="P27">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,30 +229,30 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,10 +262,13 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
-    <t>Dubočica</t>
+    <t>Tekstilac Odžaci</t>
   </si>
   <si>
     <t>Tukums</t>
@@ -274,7 +277,7 @@
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Tekstilac Odžaci</t>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
@@ -283,67 +286,67 @@
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
-    <t>Haras El Hodood</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
     <t>Olympique Béja</t>
   </si>
   <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Huntsville City</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
+    <t>AS Slimane</t>
   </si>
   <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
-    <t>FAP</t>
+    <t>Semendrija 1924</t>
   </si>
   <si>
     <t>Ogre United</t>
@@ -352,7 +355,7 @@
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>Spaeri</t>
@@ -361,58 +364,55 @@
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
+    <t>Masr</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Masr</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
+    <t>Gabès</t>
   </si>
   <si>
     <t>Club Africain</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Gabès</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1017,13 +1017,13 @@
         <v>133</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1572,13 +1572,13 @@
         <v>133</v>
       </c>
       <c r="P5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -1757,13 +1757,13 @@
         <v>133</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1796,40 +1796,40 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO6">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,133 +2682,133 @@
         <v>133</v>
       </c>
       <c r="P11">
+        <v>3.5</v>
+      </c>
+      <c r="Q11">
+        <v>2.9</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11">
+        <v>4.81</v>
+      </c>
+      <c r="T11">
+        <v>1.85</v>
+      </c>
+      <c r="U11">
+        <v>2.81</v>
+      </c>
+      <c r="V11">
+        <v>1.56</v>
+      </c>
+      <c r="W11">
+        <v>2.26</v>
+      </c>
+      <c r="X11">
+        <v>3.68</v>
+      </c>
+      <c r="Y11">
+        <v>1.2</v>
+      </c>
+      <c r="Z11">
+        <v>10</v>
+      </c>
+      <c r="AA11">
+        <v>1.02</v>
+      </c>
+      <c r="AB11">
+        <v>1.06</v>
+      </c>
+      <c r="AC11">
+        <v>1.52</v>
+      </c>
+      <c r="AD11">
+        <v>2.36</v>
+      </c>
+      <c r="AE11">
+        <v>2.56</v>
+      </c>
+      <c r="AF11">
+        <v>1.4</v>
+      </c>
+      <c r="AG11">
+        <v>5.15</v>
+      </c>
+      <c r="AH11">
+        <v>1.1</v>
+      </c>
+      <c r="AI11">
+        <v>11</v>
+      </c>
+      <c r="AJ11">
+        <v>1.01</v>
+      </c>
+      <c r="AK11">
+        <v>2.19</v>
+      </c>
+      <c r="AL11">
         <v>1.59</v>
       </c>
-      <c r="Q11">
-        <v>3.85</v>
-      </c>
-      <c r="R11">
-        <v>4.93</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT11">
         <v>0</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY11">
         <v>0</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>133</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,22 +3052,22 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3076,10 +3076,10 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3091,40 +3091,40 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD13">
         <v>0</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3237,13 +3237,13 @@
         <v>133</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -3938,10 +3938,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4344,7 +4344,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4717,13 +4717,13 @@
         <v>133</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>102</v>
@@ -4902,13 +4902,13 @@
         <v>133</v>
       </c>
       <c r="P23">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -232,27 +232,27 @@
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,30 +262,30 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
+    <t>Difaâ El Jadida</t>
+  </si>
+  <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
@@ -304,66 +304,66 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
     <t>Olympique Béja</t>
   </si>
   <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
   </si>
   <si>
     <t>Kairouan</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
     <t>Spaeri</t>
   </si>
   <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
@@ -382,37 +382,37 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>Métlaoui</t>
   </si>
   <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Gabès</t>
   </si>
   <si>
     <t>Monastir</t>
   </si>
   <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
     <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2276,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>88</v>
@@ -2461,7 +2461,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3568,7 +3568,7 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -4126,7 +4126,7 @@
         <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>98</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -4529,7 +4529,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4717,13 +4717,13 @@
         <v>133</v>
       </c>
       <c r="P22">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -5048,10 +5048,10 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
         <v>103</v>
@@ -5087,13 +5087,13 @@
         <v>133</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5233,10 +5233,10 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>104</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -229,15 +229,15 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
@@ -247,12 +247,12 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,157 +262,157 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tekstilac Odžaci</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Difaâ El Jadida</t>
   </si>
   <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Difaâ El Jadida</t>
-  </si>
-  <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
+    <t>Auda</t>
+  </si>
+  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Auda</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
   </si>
   <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Semendrija 1924</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
-    <t>FAP</t>
+    <t>Spaeri</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
     <t>Masr</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Grobiņa</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
   </si>
   <si>
     <t>Club Africain</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1017,13 +1017,13 @@
         <v>133</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R2">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -1533,10 +1533,10 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -1572,13 +1572,13 @@
         <v>133</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1611,40 +1611,40 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO5">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -1757,13 +1757,13 @@
         <v>133</v>
       </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1796,40 +1796,40 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL6">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -2127,133 +2127,133 @@
         <v>133</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU8">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV8">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW8">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY8">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
@@ -2497,133 +2497,133 @@
         <v>133</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
         <v>4.81</v>
@@ -2733,7 +2733,7 @@
         <v>1.4</v>
       </c>
       <c r="AG11">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AH11">
         <v>1.1</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -2867,22 +2867,22 @@
         <v>133</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="R12">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -2891,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
@@ -3052,22 +3052,22 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q13">
-        <v>3.85</v>
+        <v>3.26</v>
       </c>
       <c r="R13">
-        <v>4.93</v>
+        <v>5.25</v>
       </c>
       <c r="S13">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3076,10 +3076,10 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3091,40 +3091,40 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="BC13">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD13">
         <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3237,13 +3237,13 @@
         <v>133</v>
       </c>
       <c r="P14">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3422,13 +3422,13 @@
         <v>133</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -3938,10 +3938,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4123,10 +4123,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>98</v>
@@ -4496,7 +4496,7 @@
         <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>100</v>
@@ -4529,16 +4529,16 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -5048,10 +5048,10 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
         <v>103</v>
@@ -5087,13 +5087,13 @@
         <v>133</v>
       </c>
       <c r="P24">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P26">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -241,6 +241,9 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
@@ -250,9 +253,6 @@
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,21 +262,21 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
@@ -286,75 +286,75 @@
     <t>ŁKS Łódź</t>
   </si>
   <si>
+    <t>Auda</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
-    <t>Auda</t>
-  </si>
-  <si>
-    <t>National Bank of Egypt</t>
+    <t>Al Shabab</t>
   </si>
   <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Shabab</t>
-  </si>
-  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Stade Tunisien</t>
   </si>
   <si>
-    <t>Kairouan</t>
+    <t>Zarzis</t>
   </si>
   <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
     <t>FAP</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Ogre United</t>
-  </si>
-  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
     <t>Spaeri</t>
   </si>
   <si>
@@ -364,55 +364,55 @@
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
     <t>Masr</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
-    <t>Ismaily SC</t>
+    <t>Al Nassr</t>
   </si>
   <si>
     <t>UTS Rabat</t>
   </si>
   <si>
-    <t>Al Nassr</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
     <t>CS Sfaxien</t>
   </si>
   <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
-    <t>Monastir</t>
+    <t>Métlaoui</t>
   </si>
   <si>
     <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1017,133 +1017,133 @@
         <v>133</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q2">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R2">
         <v>3.7</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT2">
         <v>0</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY2">
         <v>0</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>3.18</v>
       </c>
       <c r="X10">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Y10">
         <v>1.49</v>
@@ -2536,7 +2536,7 @@
         <v>1.02</v>
       </c>
       <c r="AC10">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AD10">
         <v>4.05</v>
@@ -2548,7 +2548,7 @@
         <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AH10">
         <v>1.45</v>
@@ -2643,10 +2643,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
@@ -2682,133 +2682,133 @@
         <v>133</v>
       </c>
       <c r="P11">
-        <v>3.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>4.93</v>
       </c>
       <c r="S11">
-        <v>4.81</v>
+        <v>2.04</v>
       </c>
       <c r="T11">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="U11">
-        <v>2.81</v>
+        <v>4.9</v>
       </c>
       <c r="V11">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>3.68</v>
+        <v>2.28</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AD11">
-        <v>2.36</v>
+        <v>3.95</v>
       </c>
       <c r="AE11">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="AF11">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AG11">
-        <v>5.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH11">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AI11">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AJ11">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="AL11">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AM11">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AN11">
-        <v>1.21</v>
+        <v>2.08</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT11">
         <v>0</v>
       </c>
       <c r="AU11">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY11">
         <v>0</v>
       </c>
       <c r="AZ11">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="BD11">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="BF11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
@@ -2867,133 +2867,133 @@
         <v>133</v>
       </c>
       <c r="P12">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="S12">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="T12">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="U12">
-        <v>4.9</v>
+        <v>6.27</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X12">
-        <v>2.28</v>
+        <v>3.32</v>
       </c>
       <c r="Y12">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC12">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AD12">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="AE12">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="AF12">
+        <v>1.55</v>
+      </c>
+      <c r="AG12">
+        <v>4.3</v>
+      </c>
+      <c r="AH12">
+        <v>1.15</v>
+      </c>
+      <c r="AI12">
+        <v>9</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>2.15</v>
+      </c>
+      <c r="AL12">
+        <v>1.61</v>
+      </c>
+      <c r="AM12">
+        <v>1.25</v>
+      </c>
+      <c r="AN12">
+        <v>2.01</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1.38</v>
+      </c>
+      <c r="AQ12">
+        <v>1.66</v>
+      </c>
+      <c r="AR12">
         <v>2.07</v>
       </c>
-      <c r="AG12">
-        <v>2.55</v>
-      </c>
-      <c r="AH12">
-        <v>1.41</v>
-      </c>
-      <c r="AI12">
-        <v>4.4</v>
-      </c>
-      <c r="AJ12">
-        <v>1.15</v>
-      </c>
-      <c r="AK12">
-        <v>1.63</v>
-      </c>
-      <c r="AL12">
-        <v>2</v>
-      </c>
-      <c r="AM12">
-        <v>1.17</v>
-      </c>
-      <c r="AN12">
-        <v>2.08</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC12">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE12">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3052,133 +3052,133 @@
         <v>133</v>
       </c>
       <c r="P13">
-        <v>1.66</v>
+        <v>3.8</v>
       </c>
       <c r="Q13">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>5.25</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT13">
         <v>0</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY13">
         <v>0</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
@@ -3237,133 +3237,133 @@
         <v>133</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -3422,13 +3422,13 @@
         <v>133</v>
       </c>
       <c r="P15">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -3789,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -4123,7 +4123,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>79</v>
@@ -4308,7 +4308,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -4493,10 +4493,10 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
         <v>100</v>
@@ -4532,13 +4532,13 @@
         <v>133</v>
       </c>
       <c r="P21">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -4678,10 +4678,10 @@
         <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
@@ -4863,7 +4863,7 @@
         <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>79</v>
@@ -5048,7 +5048,7 @@
         <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>79</v>
@@ -5233,7 +5233,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>79</v>
@@ -5418,7 +5418,7 @@
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>79</v>
@@ -5454,7 +5454,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5603,10 +5603,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
         <v>106</v>
@@ -5642,79 +5642,79 @@
         <v>133</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -5756,19 +5756,19 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG27">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
   <si>
     <t>Date</t>
   </si>
@@ -214,6 +214,9 @@
     <t>15:00</t>
   </si>
   <si>
+    <t>16:00</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -229,6 +232,9 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
@@ -241,18 +247,18 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -262,18 +268,24 @@
     <t>El Geish</t>
   </si>
   <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
     <t>Borac Čačak</t>
   </si>
   <si>
-    <t>Dinamo Jug</t>
-  </si>
-  <si>
     <t>Tukums</t>
   </si>
   <si>
     <t>Dubočica</t>
   </si>
   <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
@@ -289,69 +301,78 @@
     <t>Auda</t>
   </si>
   <si>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
+    <t>MC Oran</t>
   </si>
   <si>
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Olympique Béja</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
     <t>Kairouan</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Olympique Béja</t>
+    <t>Stade Tunisien</t>
   </si>
   <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
     <t>Ogre United</t>
   </si>
   <si>
     <t>FAP</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
@@ -367,52 +388,55 @@
     <t>Grobiņa</t>
   </si>
   <si>
+    <t>Masr</t>
+  </si>
+  <si>
     <t>Ismaily SC</t>
   </si>
   <si>
-    <t>Masr</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Al Nassr</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
+    <t>ASO Chlef</t>
   </si>
   <si>
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
     <t>SV Stripfing Weiden</t>
   </si>
   <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
     <t>Monastir</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
     <t>CS Sfaxien</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
+    <t>Ben Guerdane</t>
   </si>
   <si>
     <t>Club Africain</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -782,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI27"/>
+  <dimension ref="A1:BI30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -978,16 +1002,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1014,7 +1038,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P2">
         <v>2.25</v>
@@ -1163,16 +1187,16 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1199,7 +1223,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1348,16 +1372,16 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1384,7 +1408,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1533,16 +1557,16 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1569,7 +1593,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P5">
         <v>1.91</v>
@@ -1718,16 +1742,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1754,7 +1778,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1903,16 +1927,16 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1939,7 +1963,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2085,19 +2109,19 @@
         <v>46149</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2124,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2262,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3">
-        <v>46149.54166666666</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -2270,19 +2294,19 @@
         <v>46149</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2309,7 +2333,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2447,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3">
-        <v>46149.54166666666</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -2461,13 +2485,13 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2494,136 +2518,136 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2640,19 +2664,19 @@
         <v>46149</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2679,25 +2703,25 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2706,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2721,40 +2745,40 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -2799,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="BC11">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD11">
         <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF11">
         <v>0</v>
@@ -2817,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3">
-        <v>46149.58333333334</v>
+        <v>46149.54166666666</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -2825,19 +2849,19 @@
         <v>46149</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2864,136 +2888,136 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P12">
         <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="S12">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T12">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="U12">
-        <v>6.27</v>
+        <v>4.64</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="X12">
-        <v>3.32</v>
+        <v>2.36</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="Z12">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AA12">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB12">
+        <v>1.02</v>
+      </c>
+      <c r="AC12">
+        <v>1.16</v>
+      </c>
+      <c r="AD12">
+        <v>4.05</v>
+      </c>
+      <c r="AE12">
+        <v>1.61</v>
+      </c>
+      <c r="AF12">
+        <v>2.25</v>
+      </c>
+      <c r="AG12">
+        <v>2.65</v>
+      </c>
+      <c r="AH12">
+        <v>1.45</v>
+      </c>
+      <c r="AI12">
+        <v>4.65</v>
+      </c>
+      <c r="AJ12">
+        <v>1.12</v>
+      </c>
+      <c r="AK12">
+        <v>1.61</v>
+      </c>
+      <c r="AL12">
+        <v>2.16</v>
+      </c>
+      <c r="AM12">
+        <v>1.19</v>
+      </c>
+      <c r="AN12">
+        <v>1.92</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
         <v>1.08</v>
       </c>
-      <c r="AC12">
-        <v>1.38</v>
-      </c>
-      <c r="AD12">
-        <v>2.62</v>
-      </c>
-      <c r="AE12">
-        <v>2.29</v>
-      </c>
-      <c r="AF12">
-        <v>1.55</v>
-      </c>
-      <c r="AG12">
-        <v>4.3</v>
-      </c>
-      <c r="AH12">
-        <v>1.15</v>
-      </c>
-      <c r="AI12">
-        <v>9</v>
-      </c>
-      <c r="AJ12">
-        <v>1</v>
-      </c>
-      <c r="AK12">
-        <v>2.15</v>
-      </c>
-      <c r="AL12">
+      <c r="AQ12">
+        <v>1.23</v>
+      </c>
+      <c r="AR12">
         <v>1.61</v>
       </c>
-      <c r="AM12">
-        <v>1.25</v>
-      </c>
-      <c r="AN12">
-        <v>2.01</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.38</v>
-      </c>
-      <c r="AQ12">
-        <v>1.66</v>
-      </c>
-      <c r="AR12">
-        <v>2.07</v>
-      </c>
       <c r="AS12">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="AT12">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AU12">
-        <v>2.7</v>
+        <v>5.08</v>
       </c>
       <c r="AV12">
-        <v>2.06</v>
+        <v>3.42</v>
       </c>
       <c r="AW12">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="AX12">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AY12">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AZ12">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="BA12">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BB12">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BC12">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="BD12">
-        <v>3.18</v>
+        <v>4.6</v>
       </c>
       <c r="BE12">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="BF12">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3002,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3">
-        <v>46149.58333333334</v>
+        <v>46149.54166666666</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -3013,16 +3037,16 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3049,136 +3073,136 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P13">
-        <v>3.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>4.93</v>
       </c>
       <c r="S13">
-        <v>4.76</v>
+        <v>2.04</v>
       </c>
       <c r="T13">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="U13">
-        <v>2.83</v>
+        <v>4.9</v>
       </c>
       <c r="V13">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>3.68</v>
+        <v>2.28</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AD13">
-        <v>2.36</v>
+        <v>3.95</v>
       </c>
       <c r="AE13">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="AF13">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AG13">
-        <v>5.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH13">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AI13">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AJ13">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK13">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="AL13">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AM13">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="AN13">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT13">
         <v>0</v>
       </c>
       <c r="AU13">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY13">
         <v>0</v>
       </c>
       <c r="AZ13">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="BD13">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="BF13">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3195,19 +3219,19 @@
         <v>46149</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3234,136 +3258,136 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P14">
-        <v>5.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q14">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>5.3</v>
+        <v>4.76</v>
       </c>
       <c r="T14">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="U14">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="V14">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
-        <v>3.58</v>
+        <v>2.26</v>
       </c>
       <c r="X14">
-        <v>2.11</v>
+        <v>3.68</v>
       </c>
       <c r="Y14">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA14">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AB14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC14">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AD14">
-        <v>4.71</v>
+        <v>2.36</v>
       </c>
       <c r="AE14">
-        <v>1.42</v>
+        <v>2.66</v>
       </c>
       <c r="AF14">
-        <v>2.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG14">
-        <v>2.14</v>
+        <v>5.2</v>
       </c>
       <c r="AH14">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="AI14">
-        <v>3.34</v>
+        <v>11</v>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AK14">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="AL14">
-        <v>2.23</v>
+        <v>1.59</v>
       </c>
       <c r="AM14">
-        <v>1.16</v>
+        <v>1.63</v>
       </c>
       <c r="AN14">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AR14">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="AS14">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AT14">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="AV14">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="AW14">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="AX14">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AY14">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="BA14">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="BB14">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="BC14">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="BD14">
-        <v>5.1</v>
+        <v>2.82</v>
       </c>
       <c r="BE14">
-        <v>2.33</v>
+        <v>1.38</v>
       </c>
       <c r="BF14">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3372,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -3380,19 +3404,19 @@
         <v>46149</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3419,136 +3443,136 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3557,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -3565,19 +3589,19 @@
         <v>46149</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3604,7 +3628,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3742,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3">
-        <v>46149.70833333334</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3750,19 +3774,19 @@
         <v>46149</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3789,136 +3813,136 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -3927,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3">
-        <v>46149.875</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="18" spans="1:61">
@@ -3935,19 +3959,19 @@
         <v>46149</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3974,7 +3998,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4112,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3">
-        <v>46149.875</v>
+        <v>46149.66666666666</v>
       </c>
     </row>
     <row r="19" spans="1:61">
@@ -4123,16 +4147,16 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4159,7 +4183,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4297,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3">
-        <v>46149.875</v>
+        <v>46149.70833333334</v>
       </c>
     </row>
     <row r="20" spans="1:61">
@@ -4305,19 +4329,19 @@
         <v>46149</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4344,7 +4368,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4490,19 +4514,19 @@
         <v>46149</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4529,82 +4553,82 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -4646,19 +4670,19 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -4675,19 +4699,19 @@
         <v>46149</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
         <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4714,7 +4738,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4860,19 +4884,19 @@
         <v>46149</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4899,7 +4923,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5045,19 +5069,19 @@
         <v>46149</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5084,7 +5108,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5230,19 +5254,19 @@
         <v>46149</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5269,7 +5293,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5415,19 +5439,19 @@
         <v>46149</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5454,7 +5478,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5600,19 +5624,19 @@
         <v>46149</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5639,82 +5663,82 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P27">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -5756,19 +5780,19 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -5777,6 +5801,561 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61">
+      <c r="A28" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>-1</v>
+      </c>
+      <c r="N28">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>141</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:61">
+      <c r="A29" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>-1</v>
+      </c>
+      <c r="N29">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="s">
+        <v>141</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61">
+      <c r="A30" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>-1</v>
+      </c>
+      <c r="N30">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>141</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="3">
         <v>46149.875</v>
       </c>
     </row>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="148">
   <si>
     <t>Date</t>
   </si>
@@ -229,19 +229,22 @@
     <t>Serbia Prva Liga</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
+    <t>Turkey 1. Lig</t>
   </si>
   <si>
     <t>Saudi Arabia Professional League</t>
@@ -250,15 +253,15 @@
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Austria 2. Liga</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Austria 2. Liga</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -274,34 +277,40 @@
     <t>Borac Čačak</t>
   </si>
   <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
     <t>Tukums</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
     <t>ES Mostaganem</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
+    <t>BB Bodrumspor</t>
+  </si>
+  <si>
+    <t>Haras El Hodood</t>
   </si>
   <si>
     <t>Auda</t>
   </si>
   <si>
-    <t>Haras El Hodood</t>
+    <t>Çorum Belediyespor</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
@@ -319,39 +328,39 @@
     <t>FAR Rabat</t>
   </si>
   <si>
+    <t>Kairouan</t>
+  </si>
+  <si>
+    <t>AS Slimane</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Floridsdorfer AC</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Olympique Béja</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Stade Tunisien</t>
+  </si>
+  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
-    <t>AS Slimane</t>
-  </si>
-  <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Floridsdorfer AC</t>
-  </si>
-  <si>
-    <t>Kairouan</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
-    <t>Stade Tunisien</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
@@ -361,34 +370,40 @@
     <t>Grafičar</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
     <t>Ogre United</t>
   </si>
   <si>
-    <t>FAP</t>
-  </si>
-  <si>
     <t>JS Saoura</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
     <t>Semendrija 1924</t>
   </si>
   <si>
     <t>Spaeri</t>
   </si>
   <si>
+    <t>Pogoń Grod. Mazowiecki</t>
+  </si>
+  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
+    <t>Pendikspor</t>
+  </si>
+  <si>
+    <t>Masr</t>
   </si>
   <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Masr</t>
+    <t>Keçiörengücü</t>
   </si>
   <si>
     <t>Ismaily SC</t>
@@ -406,37 +421,37 @@
     <t>Olympic Safi</t>
   </si>
   <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Gabès</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>SV Stripfing Weiden</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>CS Sfaxien</t>
+  </si>
+  <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
+    <t>Club Africain</t>
+  </si>
+  <si>
+    <t>Ben Guerdane</t>
+  </si>
+  <si>
     <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Gabès</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
-    <t>SV Stripfing Weiden</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>CS Sfaxien</t>
-  </si>
-  <si>
-    <t>Ben Guerdane</t>
-  </si>
-  <si>
-    <t>Club Africain</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -806,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI30"/>
+  <dimension ref="A1:BI32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1005,13 +1020,13 @@
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1038,7 +1053,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P2">
         <v>2.25</v>
@@ -1190,13 +1205,13 @@
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1223,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1375,13 +1390,13 @@
         <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1408,7 +1423,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1563,10 +1578,10 @@
         <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1593,16 +1608,16 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1635,40 +1650,40 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>0</v>
@@ -1745,13 +1760,13 @@
         <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1778,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1930,13 +1945,13 @@
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1963,16 +1978,16 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -2005,40 +2020,40 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2112,16 +2127,16 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2148,7 +2163,7 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2300,13 +2315,13 @@
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2333,7 +2348,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2485,13 +2500,13 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2518,7 +2533,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2670,13 +2685,13 @@
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2703,136 +2718,136 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -2855,13 +2870,13 @@
         <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2888,136 +2903,136 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P12">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU12">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV12">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX12">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ12">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD12">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3037,16 +3052,16 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
         <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3073,25 +3088,25 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3100,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3115,40 +3130,40 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3193,13 +3208,13 @@
         <v>0</v>
       </c>
       <c r="BC13">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BD13">
         <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3225,13 +3240,13 @@
         <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3258,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P14">
         <v>3.8</v>
@@ -3407,16 +3422,16 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3443,136 +3458,136 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P15">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="Q15">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="R15">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="S15">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="T15">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>6.27</v>
+        <v>4.9</v>
       </c>
       <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>2.28</v>
+      </c>
+      <c r="Y15">
         <v>1.48</v>
       </c>
-      <c r="W15">
-        <v>2.38</v>
-      </c>
-      <c r="X15">
-        <v>3.32</v>
-      </c>
-      <c r="Y15">
-        <v>1.26</v>
-      </c>
       <c r="Z15">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AD15">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="AE15">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="AG15">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH15">
+        <v>1.41</v>
+      </c>
+      <c r="AI15">
+        <v>4.4</v>
+      </c>
+      <c r="AJ15">
         <v>1.15</v>
       </c>
-      <c r="AI15">
-        <v>9</v>
-      </c>
-      <c r="AJ15">
-        <v>1</v>
-      </c>
       <c r="AK15">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AL15">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AM15">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AN15">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="BD15">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="BF15">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3589,19 +3604,19 @@
         <v>46149</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3628,7 +3643,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3766,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3774,19 +3789,19 @@
         <v>46149</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3813,136 +3828,136 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P17">
-        <v>5.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q17">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="R17">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="S17">
-        <v>5.3</v>
+        <v>2.34</v>
       </c>
       <c r="T17">
-        <v>2.54</v>
+        <v>1.93</v>
       </c>
       <c r="U17">
-        <v>1.87</v>
+        <v>6.27</v>
       </c>
       <c r="V17">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>3.58</v>
+        <v>2.38</v>
       </c>
       <c r="X17">
-        <v>2.11</v>
+        <v>3.32</v>
       </c>
       <c r="Y17">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA17">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AB17">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC17">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AD17">
-        <v>4.71</v>
+        <v>2.62</v>
       </c>
       <c r="AE17">
-        <v>1.42</v>
+        <v>2.29</v>
       </c>
       <c r="AF17">
-        <v>2.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="AH17">
+        <v>1.15</v>
+      </c>
+      <c r="AI17">
+        <v>9</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>2.15</v>
+      </c>
+      <c r="AL17">
+        <v>1.61</v>
+      </c>
+      <c r="AM17">
+        <v>1.25</v>
+      </c>
+      <c r="AN17">
+        <v>2.01</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1.38</v>
+      </c>
+      <c r="AQ17">
         <v>1.66</v>
       </c>
-      <c r="AI17">
-        <v>3.34</v>
-      </c>
-      <c r="AJ17">
-        <v>1.24</v>
-      </c>
-      <c r="AK17">
-        <v>1.57</v>
-      </c>
-      <c r="AL17">
-        <v>2.23</v>
-      </c>
-      <c r="AM17">
-        <v>1.16</v>
-      </c>
-      <c r="AN17">
-        <v>1.11</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>1.2</v>
-      </c>
-      <c r="AQ17">
-        <v>1.36</v>
-      </c>
       <c r="AR17">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AS17">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AT17">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AU17">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AV17">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AW17">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AX17">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AY17">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AZ17">
-        <v>3.3</v>
+        <v>1.38</v>
       </c>
       <c r="BA17">
-        <v>1.41</v>
+        <v>3.2</v>
       </c>
       <c r="BB17">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="BC17">
-        <v>1.55</v>
+        <v>2.41</v>
       </c>
       <c r="BD17">
-        <v>5.1</v>
+        <v>3.18</v>
       </c>
       <c r="BE17">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="BF17">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -3951,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="18" spans="1:61">
@@ -3959,19 +3974,19 @@
         <v>46149</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3998,7 +4013,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4136,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3">
-        <v>46149.66666666666</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="19" spans="1:61">
@@ -4144,19 +4159,19 @@
         <v>46149</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4183,136 +4198,136 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO19">
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG19">
         <v>0</v>
@@ -4321,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3">
-        <v>46149.70833333334</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="20" spans="1:61">
@@ -4329,19 +4344,19 @@
         <v>46149</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4368,7 +4383,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4506,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3">
-        <v>46149.875</v>
+        <v>46149.66666666666</v>
       </c>
     </row>
     <row r="21" spans="1:61">
@@ -4514,19 +4529,19 @@
         <v>46149</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4553,82 +4568,82 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P21">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -4670,19 +4685,19 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -4691,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3">
-        <v>46149.875</v>
+        <v>46149.70833333334</v>
       </c>
     </row>
     <row r="22" spans="1:61">
@@ -4702,16 +4717,16 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4738,7 +4753,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4887,16 +4902,16 @@
         <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4923,7 +4938,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5072,16 +5087,16 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5108,7 +5123,7 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5257,16 +5272,16 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5293,7 +5308,7 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5442,16 +5457,16 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5478,7 +5493,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5627,16 +5642,16 @@
         <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>82</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5663,7 +5678,7 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5812,16 +5827,16 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5848,7 +5863,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5997,16 +6012,16 @@
         <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6033,7 +6048,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6182,16 +6197,16 @@
         <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6218,7 +6233,7 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -6356,6 +6371,376 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61">
+      <c r="A31" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>-1</v>
+      </c>
+      <c r="N31">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>146</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31">
+        <v>0</v>
+      </c>
+      <c r="AW31">
+        <v>0</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3">
+        <v>46149.875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61">
+      <c r="A32" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>-1</v>
+      </c>
+      <c r="N32">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>146</v>
+      </c>
+      <c r="P32">
+        <v>1.9</v>
+      </c>
+      <c r="Q32">
+        <v>3.6</v>
+      </c>
+      <c r="R32">
+        <v>3.5</v>
+      </c>
+      <c r="S32">
+        <v>2.43</v>
+      </c>
+      <c r="T32">
+        <v>2.2</v>
+      </c>
+      <c r="U32">
+        <v>4.2</v>
+      </c>
+      <c r="V32">
+        <v>1.32</v>
+      </c>
+      <c r="W32">
+        <v>3.02</v>
+      </c>
+      <c r="X32">
+        <v>2.65</v>
+      </c>
+      <c r="Y32">
+        <v>1.44</v>
+      </c>
+      <c r="Z32">
+        <v>5.7</v>
+      </c>
+      <c r="AA32">
+        <v>1.08</v>
+      </c>
+      <c r="AB32">
+        <v>1.01</v>
+      </c>
+      <c r="AC32">
+        <v>1.21</v>
+      </c>
+      <c r="AD32">
+        <v>3.58</v>
+      </c>
+      <c r="AE32">
+        <v>1.78</v>
+      </c>
+      <c r="AF32">
+        <v>1.98</v>
+      </c>
+      <c r="AG32">
+        <v>2.45</v>
+      </c>
+      <c r="AH32">
+        <v>1.34</v>
+      </c>
+      <c r="AI32">
+        <v>5.05</v>
+      </c>
+      <c r="AJ32">
+        <v>1.1</v>
+      </c>
+      <c r="AK32">
+        <v>1.64</v>
+      </c>
+      <c r="AL32">
+        <v>2.1</v>
+      </c>
+      <c r="AM32">
+        <v>1.22</v>
+      </c>
+      <c r="AN32">
+        <v>1.61</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>1.18</v>
+      </c>
+      <c r="BC32">
+        <v>1.98</v>
+      </c>
+      <c r="BD32">
+        <v>3.92</v>
+      </c>
+      <c r="BE32">
+        <v>1.73</v>
+      </c>
+      <c r="BF32">
+        <v>1.17</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3">
         <v>46149.875</v>
       </c>
     </row>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1234,40 +1234,40 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1431,40 +1431,40 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="S13" t="n">
-        <v>4.76</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U13" t="n">
-        <v>2.83</v>
+        <v>6.27</v>
       </c>
       <c r="V13" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.4</v>
       </c>
-      <c r="AG13" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.48</v>
+        <v>1.38</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>2.34</v>
+        <v>4.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>6.27</v>
+        <v>2.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="X14" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3371,70 +3371,70 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.81</v>
+        <v>5.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V18" t="n">
         <v>1.21</v>
@@ -3977,55 +3977,55 @@
         <v>3.58</v>
       </c>
       <c r="X18" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="n">
         <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>1.41</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="BF18" t="n">
         <v>1.29</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1234,40 +1234,40 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>4.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>6.27</v>
+        <v>2.83</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="X13" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
-        <v>4.76</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>2.83</v>
+        <v>6.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X14" t="n">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1.4</v>
       </c>
-      <c r="AG14" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.48</v>
+        <v>1.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="X15" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X16" t="n">
-        <v>2.28</v>
+        <v>2.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>4.75</v>
+        <v>4.93</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.17</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,73 +3953,73 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q18" t="n">
         <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="X18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
         <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AM18" t="n">
         <v>1.18</v>
@@ -4031,55 +4031,55 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="BA18" t="n">
         <v>1.41</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1825,40 +1825,40 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4.76</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.85</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AF13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.11</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK13" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.77</v>
+        <v>2.28</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AL17" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE17" t="n">
+      <c r="AM17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA17" t="n">
         <v>1.63</v>
       </c>
-      <c r="AF17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1234,40 +1234,40 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,40 +2219,40 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.77</v>
+        <v>2.28</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AI13" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AL16" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AM16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA16" t="n">
         <v>1.63</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.76</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.85</v>
       </c>
-      <c r="U17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AF17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.11</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
         <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="X2" t="n">
         <v>4.2</v>
@@ -831,28 +831,28 @@
         <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
         <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
         <v>2.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.34</v>
+        <v>2.97</v>
       </c>
       <c r="AF2" t="n">
         <v>1.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AH2" t="n">
         <v>1.07</v>
@@ -864,16 +864,16 @@
         <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>2.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BC2" t="n">
         <v>2.96</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1234,40 +1234,40 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>4.93</v>
+        <v>2.8</v>
       </c>
       <c r="S13" t="n">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
-        <v>2.28</v>
+        <v>3.58</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.95</v>
+        <v>2.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.55</v>
+        <v>4.95</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>6.27</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="X14" t="n">
-        <v>3.32</v>
+        <v>2.77</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
         <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.29</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3365,76 +3365,76 @@
         <v>1.55</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD15" t="n">
         <v>3.9</v>
       </c>
-      <c r="R15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U15" t="n">
-        <v>5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
         <v>4.8</v>
       </c>
       <c r="AJ15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
         <v>1.17</v>
       </c>
-      <c r="AK15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AN15" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BE15" t="n">
         <v>1.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="S16" t="n">
-        <v>4.76</v>
+        <v>2.33</v>
       </c>
       <c r="T16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>2.83</v>
+        <v>5.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X16" t="n">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AG16" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.48</v>
+        <v>1.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P31" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,7 +873,7 @@
         <v>1.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>2.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BC2" t="n">
         <v>2.96</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46149.5</v>
+        <v>46149.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46149.54166666666</v>
+        <v>46149.5</v>
       </c>
     </row>
     <row r="11">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46149.58333333334</v>
+        <v>46149.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,70 +3174,70 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46149.58333333334</v>
+        <v>46149.5625</v>
       </c>
     </row>
     <row r="15">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
         <v>3.04</v>
       </c>
       <c r="X15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA15" t="n">
         <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.8</v>
+        <v>4.96</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.33</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="X16" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AU16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA16" t="n">
         <v>2.7</v>
       </c>
-      <c r="AV16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BB16" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3759,76 +3759,76 @@
         <v>1.55</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD17" t="n">
         <v>3.9</v>
       </c>
-      <c r="R17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
         <v>4.8</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.17</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BE17" t="n">
         <v>1.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,134 +4150,134 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z19" t="n">
         <v>6.5</v>
       </c>
-      <c r="Q19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.18</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BG19" t="n">
         <v>0</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46149.625</v>
+        <v>46149.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46149.66666666666</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="21">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46149.70833333334</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46149.875</v>
+        <v>46149.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,1188 +5664,6 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Etoile du Sahel</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>CA Bizertin</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" s="3" t="n">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Marsa</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>CS Sfaxien</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI28" s="3" t="n">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Zarzis</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Métlaoui</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Kairouan</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Monastir</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3" t="n">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Austria 2. Liga</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Floridsdorfer AC</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>SV Stripfing Weiden</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3" t="n">
-        <v>46149.875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AS Slimane</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Gabès</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="3" t="n">
         <v>46149.875</v>
       </c>
     </row>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2577,130 +2577,130 @@
         <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2774,130 +2774,130 @@
         <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>3.32</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="AH15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI15" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM15" t="n">
+      <c r="AY15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="U16" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
       <c r="X16" t="n">
-        <v>3.58</v>
+        <v>2.46</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.47</v>
+        <v>3.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.95</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.88</v>
+        <v>4.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>5.13</v>
+        <v>3.6</v>
       </c>
       <c r="V17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.3</v>
       </c>
-      <c r="W17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI17" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="X18" t="n">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
         <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.3</v>
+        <v>2.64</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.15</v>
       </c>
-      <c r="AI18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
       <c r="AK18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AL18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="V19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX19" t="n">
         <v>1.37</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AY19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="BF19" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="X15" t="n">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.3</v>
+        <v>2.64</v>
       </c>
       <c r="AH15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.15</v>
       </c>
-      <c r="AI15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1</v>
-      </c>
       <c r="AK15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN15" t="n">
         <v>2.1</v>
       </c>
-      <c r="AL15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>5.13</v>
+        <v>5.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="X16" t="n">
-        <v>2.46</v>
+        <v>3.32</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>3.04</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.8</v>
+        <v>9.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>2.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.64</v>
+        <v>4.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.96</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
       <c r="X19" t="n">
-        <v>3.58</v>
+        <v>2.46</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.9</v>
+        <v>5.75</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.47</v>
+        <v>3.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.95</v>
+        <v>2.55</v>
       </c>
       <c r="AH19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.88</v>
+        <v>4.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.33</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="X16" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL16" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AM16" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AS16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2.65</v>
       </c>
-      <c r="AT16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.68</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X18" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
         <v>1.06</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG18" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="n">
         <v>2.15</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AM18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="BC18" t="n">
         <v>2.6</v>
       </c>
-      <c r="AV18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BD18" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
         <v>3.7</v>
@@ -4159,25 +4159,25 @@
         <v>4.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="X19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
         <v>5.75</v>
@@ -4189,19 +4189,19 @@
         <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AH19" t="n">
         <v>1.38</v>
@@ -4210,19 +4210,19 @@
         <v>4.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AM19" t="n">
         <v>1.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
         <v>1.8</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U15" t="n">
         <v>3.6</v>
       </c>
-      <c r="R15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>5</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
         <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.96</v>
+        <v>5.87</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.58</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.95</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="V17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX17" t="n">
         <v>1.37</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AY17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="BF17" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="X18" t="n">
-        <v>3.42</v>
+        <v>2.44</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.52</v>
+        <v>3.94</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.33</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>5.28</v>
+        <v>6.28</v>
       </c>
       <c r="V19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.29</v>
       </c>
-      <c r="W19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="BC19" t="n">
         <v>2.44</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="BD19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,37 +4347,37 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.75</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="AA20" t="n">
         <v>1.18</v>
@@ -4386,52 +4386,52 @@
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
         <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
         <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AS20" t="n">
         <v>2.12</v>
@@ -4458,22 +4458,22 @@
         <v>3.98</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BB20" t="n">
         <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.17</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>3.02</v>
+        <v>4.23</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="X9" t="n">
-        <v>3.38</v>
+        <v>2.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.15</v>
+        <v>3.82</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2577,130 +2577,130 @@
         <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
         <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>6.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W15" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.83</v>
       </c>
-      <c r="U17" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.95</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>11</v>
+        <v>5.87</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.21</v>
+        <v>1.56</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>5.28</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="X18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA18" t="n">
         <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>4.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
         <v>1.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
         <v>1.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U19" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.44</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.12</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.2</v>
       </c>
-      <c r="S7" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.87</v>
-      </c>
       <c r="U7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X7" t="n">
         <v>3.02</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.38</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
         <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.300000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2577,130 +2577,130 @@
         <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2774,130 +2774,130 @@
         <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
         <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>6.28</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="X15" t="n">
-        <v>3.34</v>
+        <v>2.73</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>9.199999999999999</v>
+        <v>5.87</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,80 +3756,80 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="X17" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AN17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG18" t="n">
         <v>4.33</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AH18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
         <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>4.23</v>
+        <v>4.61</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
@@ -1613,13 +1613,13 @@
         <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AA6" t="n">
         <v>1.05</v>
@@ -1634,34 +1634,34 @@
         <v>3.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AH6" t="n">
         <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,16 +1706,16 @@
         <v>1.19</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
         <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>4.72</v>
       </c>
       <c r="V11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.28</v>
       </c>
-      <c r="W11" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AD11" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BD11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.16</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD15" t="n">
         <v>2.88</v>
       </c>
-      <c r="X15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.83</v>
       </c>
-      <c r="U16" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.95</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>5.87</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.21</v>
+        <v>1.56</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4150,37 +4150,37 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
         <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>5.28</v>
+        <v>5.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="X19" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="AA19" t="n">
         <v>1.07</v>
@@ -4189,40 +4189,40 @@
         <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AM19" t="n">
         <v>1.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
         <v>1.19</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -813,16 +813,16 @@
         <v>3.36</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>5.16</v>
+        <v>5.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.2</v>
@@ -846,13 +846,13 @@
         <v>2.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AH2" t="n">
         <v>1.06</v>
@@ -870,10 +870,10 @@
         <v>1.51</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>4.17</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>4.61</v>
+        <v>3.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
-        <v>2.71</v>
+        <v>3.38</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>2.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="S9" t="n">
-        <v>4.17</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>3.02</v>
+        <v>4.61</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="X9" t="n">
-        <v>3.38</v>
+        <v>2.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2986,16 +2986,16 @@
         <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="X13" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
         <v>5.3</v>
@@ -3013,10 +3013,10 @@
         <v>4.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
         <v>2.63</v>
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>2.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG15" t="n">
         <v>4.95</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
-        <v>3.6</v>
+        <v>5.57</v>
       </c>
       <c r="V16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.36</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI16" t="n">
-        <v>5.87</v>
+        <v>4.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3795,25 +3795,25 @@
         <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
         <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH17" t="n">
         <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.15</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,37 +3953,37 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
         <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>6.28</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="X18" t="n">
-        <v>3.34</v>
+        <v>2.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.699999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="AA18" t="n">
         <v>1.04</v>
@@ -3992,94 +3992,94 @@
         <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC18" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="W19" t="n">
-        <v>2.97</v>
+        <v>2.24</v>
       </c>
       <c r="X19" t="n">
-        <v>2.47</v>
+        <v>3.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4365,22 +4365,22 @@
         <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AB20" t="n">
         <v>1.01</v>
@@ -4392,10 +4392,10 @@
         <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AG20" t="n">
         <v>1.85</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="S26" t="n">
         <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="X26" t="n">
         <v>2.5</v>
@@ -5559,7 +5559,7 @@
         <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AA26" t="n">
         <v>1.08</v>
@@ -5577,7 +5577,7 @@
         <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
         <v>2.74</v>
@@ -5586,13 +5586,13 @@
         <v>1.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL26" t="n">
         <v>2.1</v>
@@ -5646,16 +5646,16 @@
         <v>1.18</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BD26" t="n">
         <v>3.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="U2" t="n">
-        <v>5.38</v>
+        <v>3.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>2.67</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.06</v>
+        <v>3.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.96</v>
+        <v>2.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>3.62</v>
+        <v>5.38</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="W3" t="n">
-        <v>2.67</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
         <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.08</v>
+        <v>2.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,80 +2180,80 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>14.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>4.61</v>
+        <v>1.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="X9" t="n">
-        <v>2.71</v>
+        <v>3.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
         <v>4</v>
@@ -3013,10 +3013,10 @@
         <v>4.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
         <v>2.63</v>
@@ -3085,13 +3085,13 @@
         <v>1.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="BD13" t="n">
         <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BF13" t="n">
         <v>1.24</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="X15" t="n">
-        <v>3.58</v>
+        <v>2.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.9</v>
+        <v>6.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.95</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
         <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD15" t="n">
         <v>3.7</v>
       </c>
-      <c r="AU15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT16" t="n">
         <v>3.7</v>
       </c>
-      <c r="R16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL17" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AM17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,80 +3953,80 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="X18" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL18" t="n">
+      <c r="AN18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AM18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U19" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>2.01</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>9.199999999999999</v>
+        <v>4.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AN19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC19" t="n">
         <v>1.9</v>
       </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BD19" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7.5</v>
-      </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="S4" t="n">
-        <v>4.17</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.02</v>
+        <v>4.61</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="X4" t="n">
-        <v>3.38</v>
+        <v>2.71</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="AH4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA11" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4</v>
+        <v>4.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="X13" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.75</v>
+        <v>6.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.16</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
         <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>6.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>2.85</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AM15" t="n">
         <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
-        <v>5.41</v>
+        <v>5.57</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>2.22</v>
+        <v>2.97</v>
       </c>
       <c r="X16" t="n">
-        <v>3.58</v>
+        <v>2.47</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.9</v>
+        <v>5.9</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.39</v>
+        <v>3.82</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI16" t="n">
         <v>4.95</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AJ16" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U17" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
         <v>3.6</v>
       </c>
-      <c r="R18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.8</v>
+        <v>6.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AM18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="BC18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT19" t="n">
         <v>3.7</v>
       </c>
-      <c r="R19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.25</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>14.3</v>
+        <v>4.17</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.72</v>
+        <v>3.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="X9" t="n">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
         <v>1.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.21</v>
+        <v>1.74</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>4.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="X11" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>6.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.16</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>5.57</v>
+        <v>3.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="X16" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.9</v>
+        <v>6.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
-        <v>2.77</v>
+        <v>3.58</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.95</v>
+        <v>9.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AM18" t="n">
         <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>5.41</v>
+        <v>5.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>2.97</v>
       </c>
       <c r="X19" t="n">
-        <v>3.58</v>
+        <v>2.47</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.9</v>
+        <v>5.9</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.39</v>
+        <v>3.82</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="AG19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI19" t="n">
         <v>4.95</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7.5</v>
-      </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1004,28 +1004,28 @@
         <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="S3" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>5.38</v>
+        <v>5.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X3" t="n">
         <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
         <v>12</v>
@@ -1037,22 +1037,22 @@
         <v>1.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>6</v>
+        <v>6.77</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI3" t="n">
         <v>15</v>
@@ -1061,10 +1061,10 @@
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AM3" t="n">
         <v>1.44</v>
@@ -1076,52 +1076,52 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.33</v>
+        <v>3.18</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
         <v>1.03</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,112 +1195,112 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5</v>
+        <v>6.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>4.61</v>
+        <v>7.09</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AA5" t="n">
         <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BF5" t="n">
         <v>1.14</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>14.3</v>
+        <v>17</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="X7" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
         <v>6.6</v>
@@ -1825,16 +1825,16 @@
         <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
         <v>3.34</v>
@@ -1849,13 +1849,13 @@
         <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.9</v>
+        <v>3.11</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AN7" t="n">
         <v>1.01</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BD7" t="n">
         <v>3.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BF7" t="n">
         <v>1.15</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,130 +2180,130 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="S9" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>3.02</v>
+        <v>3.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="X9" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AM9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.31</v>
       </c>
-      <c r="AN9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BC9" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BF9" t="n">
         <v>1.1</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD11" t="n">
         <v>4.2</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.84</v>
       </c>
-      <c r="AL11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
         <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="X12" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD13" t="n">
         <v>2.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="U15" t="n">
-        <v>6.56</v>
+        <v>5.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
         <v>1.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="AT15" t="n">
         <v>3.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AY15" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.9</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AH16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.9</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>6.16</v>
       </c>
       <c r="V17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.33</v>
       </c>
-      <c r="W17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Y18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.75</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.95</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="S19" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>5.57</v>
+        <v>3.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="X19" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.9</v>
+        <v>6.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.36</v>
       </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.33</v>
       </c>
-      <c r="AK20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7.5</v>
-      </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4750,13 +4750,13 @@
         <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T22" t="n">
         <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="V22" t="n">
         <v>1.44</v>
@@ -4765,10 +4765,10 @@
         <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
         <v>6.4</v>
@@ -4792,7 +4792,7 @@
         <v>1.76</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AH22" t="n">
         <v>1.26</v>
@@ -4819,34 +4819,34 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>6</v>
+        <v>7.37</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,113 +5135,113 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL24" t="n">
         <v>2.18</v>
       </c>
-      <c r="U24" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AM24" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD24" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AN24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AW24" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM24" t="n">
+      <c r="AX24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ24" t="n">
         <v>0</v>
       </c>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="T2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.01</v>
       </c>
-      <c r="U2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
         <v>3.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.9</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.38</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI4" t="n">
         <v>8</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,113 +1392,113 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>6.66</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>2.02</v>
+        <v>4.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>7.09</v>
+        <v>3.02</v>
       </c>
       <c r="V5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.39</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,61 +1589,61 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="S6" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
         <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" t="n">
         <v>8</v>
@@ -1652,16 +1652,16 @@
         <v>1.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>3.65</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>2.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>4.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.11</v>
+        <v>1.94</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,64 +1983,64 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
-        <v>3.76</v>
+        <v>3.13</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="U8" t="n">
-        <v>4.73</v>
+        <v>3.98</v>
       </c>
       <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.42</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AD8" t="n">
         <v>2.65</v>
       </c>
-      <c r="X8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.05</v>
@@ -2052,10 +2052,10 @@
         <v>1.72</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>3.13</v>
+        <v>4.6</v>
       </c>
       <c r="S9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS9" t="n">
         <v>2.92</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AT9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="R10" t="n">
-        <v>3.6</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
+        <v>17</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.4</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.35</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AD10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.95</v>
+        <v>6.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>3.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC10" t="n">
         <v>2.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S11" t="n">
         <v>2.15</v>
@@ -2613,28 +2613,28 @@
         <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
         <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
         <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
         <v>1.62</v>
@@ -2652,52 +2652,52 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.08</v>
+        <v>5.96</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="BB11" t="n">
         <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BD11" t="n">
         <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BF11" t="n">
         <v>1.24</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2.1</v>
       </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.91</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL13" t="n">
         <v>1.85</v>
       </c>
-      <c r="U13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AM13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>4.23</v>
+        <v>3.97</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
         <v>2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>4.87</v>
+        <v>4.93</v>
       </c>
       <c r="V14" t="n">
         <v>1.34</v>
@@ -3189,16 +3189,16 @@
         <v>2.83</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Y14" t="n">
         <v>1.39</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
         <v>1.01</v>
@@ -3207,16 +3207,16 @@
         <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AH14" t="n">
         <v>1.29</v>
@@ -3237,40 +3237,40 @@
         <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD15" t="n">
         <v>3.7</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U15" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="S16" t="n">
         <v>2.05</v>
@@ -3574,22 +3574,22 @@
         <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="X16" t="n">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA16" t="n">
         <v>1.07</v>
@@ -3598,94 +3598,94 @@
         <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AM16" t="n">
         <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.9</v>
       </c>
-      <c r="R17" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AH17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z17" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC17" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="S18" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>5.58</v>
       </c>
       <c r="V18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.33</v>
       </c>
-      <c r="W18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AN18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9</v>
+        <v>4.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>6.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="X19" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
         <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,40 +4347,40 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="R20" t="n">
-        <v>7.19</v>
+        <v>6.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="X20" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
         <v>1.06</v>
@@ -4392,13 +4392,13 @@
         <v>2.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
         <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AH20" t="n">
         <v>1.2</v>
@@ -4410,17 +4410,17 @@
         <v>1.06</v>
       </c>
       <c r="AK20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.45</v>
       </c>
-      <c r="AL20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.65</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="T21" t="n">
         <v>2.75</v>
@@ -4574,7 +4574,7 @@
         <v>1.78</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA21" t="n">
         <v>1.19</v>
@@ -4589,7 +4589,7 @@
         <v>6.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
         <v>3</v>
@@ -4622,40 +4622,40 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.57</v>
+        <v>3.97</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BB21" t="n">
         <v>1.13</v>
@@ -4941,10 +4941,10 @@
         <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>7.37</v>
+        <v>7.25</v>
       </c>
       <c r="S23" t="n">
         <v>1.95</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,112 +5135,112 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,116 +5328,116 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,83 +5525,83 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,61 +1195,61 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG4" t="n">
         <v>4</v>
       </c>
-      <c r="R4" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
         <v>8</v>
@@ -1258,16 +1258,16 @@
         <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="T6" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>4.73</v>
+        <v>5.19</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>5.55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,61 +1786,61 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>3.65</v>
+        <v>6.66</v>
       </c>
       <c r="S7" t="n">
-        <v>2.57</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>4.4</v>
+        <v>7.09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
         <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AA7" t="n">
         <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
         <v>3.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
         <v>8</v>
@@ -1849,16 +1849,16 @@
         <v>1.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.03</v>
-      </c>
       <c r="U8" t="n">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="X8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,112 +2180,112 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>4.6</v>
+        <v>3.13</v>
       </c>
       <c r="S9" t="n">
-        <v>2.21</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>5.19</v>
+        <v>3.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X11" t="n">
         <v>3.7</v>
       </c>
-      <c r="R11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.33</v>
-      </c>
       <c r="Y11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AK11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.36</v>
       </c>
-      <c r="BA11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BC11" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL12" t="n">
         <v>1.85</v>
       </c>
-      <c r="U12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AM12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="X13" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL13" t="n">
+      <c r="AN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD13" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>4.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>3.6</v>
+        <v>6.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="W15" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="X15" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
         <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AR15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS15" t="n">
         <v>2.7</v>
       </c>
-      <c r="AS15" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AT15" t="n">
-        <v>5.94</v>
+        <v>3.55</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.18</v>
+        <v>1.41</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="U16" t="n">
-        <v>5.2</v>
+        <v>5.58</v>
       </c>
       <c r="V16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.33</v>
       </c>
-      <c r="W16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AX16" t="n">
         <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.62</v>
+        <v>2.63</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.7</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BE18" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>6.16</v>
+        <v>5.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>2.43</v>
+        <v>3.04</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.06</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD20" t="n">
         <v>6.5</v>
       </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="AE20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE20" t="n">
         <v>2.15</v>
       </c>
-      <c r="U20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="BF20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.75</v>
+        <v>3.81</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="S21" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="X21" t="n">
-        <v>1.92</v>
+        <v>2.96</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.08</v>
+        <v>2.45</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.52</v>
+        <v>2.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
         <v>2.45</v>
       </c>
-      <c r="U24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="AH24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.22</v>
       </c>
-      <c r="W24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN24" t="n">
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC24" t="n">
         <v>1.91</v>
       </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,116 +5328,116 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,83 +5525,83 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>3.78</v>
       </c>
       <c r="S2" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>3.06</v>
+        <v>5.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>2.71</v>
+        <v>1.91</v>
       </c>
       <c r="X2" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG2" t="n">
-        <v>3.05</v>
+        <v>6.77</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.77</v>
+        <v>3.41</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.91</v>
+        <v>4.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.2</v>
+        <v>2.91</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>3.78</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>5.28</v>
+        <v>3.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.91</v>
+        <v>2.71</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,61 +1195,61 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>4.73</v>
+        <v>4.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
         <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
         <v>8</v>
@@ -1258,16 +1258,16 @@
         <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,112 +1392,112 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X5" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.38</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
         <v>1.39</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1509,16 +1509,16 @@
         <v>1.28</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>17</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.64</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5.19</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="X6" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
         <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AL6" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AM6" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>6.66</v>
+        <v>4.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>7.09</v>
+        <v>5.19</v>
       </c>
       <c r="V7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.39</v>
       </c>
-      <c r="W7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z7" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
         <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X8" t="n">
         <v>3.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>3.13</v>
+        <v>6.66</v>
       </c>
       <c r="S9" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>3.98</v>
+        <v>7.09</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="X9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.25</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>4.17</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>3.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
         <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
       <c r="AW10" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1.85</v>
       </c>
-      <c r="U11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AM11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="X12" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL12" t="n">
+      <c r="AN12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD12" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X13" t="n">
         <v>3.7</v>
       </c>
-      <c r="R13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.33</v>
-      </c>
       <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AK13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL13" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.36</v>
       </c>
-      <c r="BA13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.7</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="S17" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="V17" t="n">
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="X17" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
         <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AM17" t="n">
         <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AS17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA18" t="n">
         <v>2.63</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="S19" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
         <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="X19" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
         <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AM19" t="n">
         <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.7</v>
       </c>
-      <c r="AR19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BF19" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.75</v>
+        <v>3.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="S20" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>4.1</v>
+        <v>2.53</v>
       </c>
       <c r="X20" t="n">
-        <v>1.92</v>
+        <v>2.96</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.08</v>
+        <v>2.45</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.52</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>6.5</v>
       </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="AE21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE21" t="n">
         <v>2.15</v>
       </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="BF21" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,83 +5525,83 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>3.78</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>5.28</v>
+        <v>3.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.91</v>
+        <v>2.71</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.03</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG3" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.91</v>
+        <v>4.71</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,61 +1195,61 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="S4" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
         <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
         <v>8</v>
@@ -1258,16 +1258,16 @@
         <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="R5" t="n">
-        <v>3.76</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.52</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2.07</v>
       </c>
-      <c r="U5" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.25</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>4.17</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>3.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
         <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
       <c r="AW6" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>5.19</v>
+        <v>4.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
         <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.55</v>
+        <v>8</v>
       </c>
       <c r="AJ7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>3.13</v>
+        <v>4.2</v>
       </c>
       <c r="S8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.92</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X8" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.699999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>6.66</v>
+        <v>3.13</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>7.09</v>
+        <v>3.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X10" t="n">
         <v>2.9</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.38</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI10" t="n">
         <v>8</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
         <v>4</v>
@@ -2592,49 +2592,49 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="X11" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
         <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
         <v>1.83</v>
@@ -2646,7 +2646,7 @@
         <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R15" t="n">
         <v>2.9</v>
       </c>
-      <c r="R15" t="n">
-        <v>4.53</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>6.16</v>
+        <v>3.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="X15" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.300000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
         <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW15" t="n">
         <v>1.38</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AX15" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X16" t="n">
         <v>3.25</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.77</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.95</v>
+        <v>9.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.08</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>5.2</v>
+        <v>6.25</v>
       </c>
       <c r="V17" t="n">
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB17" t="n">
         <v>1.04</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE17" t="n">
+      <c r="AN17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
+      <c r="BF17" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="S18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.75</v>
       </c>
-      <c r="T18" t="n">
+      <c r="AH18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV18" t="n">
         <v>2.03</v>
       </c>
-      <c r="U18" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL18" t="n">
+      <c r="AW18" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.56</v>
       </c>
       <c r="AX18" t="n">
         <v>1.34</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.63</v>
+        <v>5.62</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,116 +5131,116 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R25" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.25</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U25" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD25" t="n">
         <v>4.2</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE25" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,83 +5525,83 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG2" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.91</v>
+        <v>4.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.6</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>4.73</v>
+        <v>4.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1312,16 +1312,16 @@
         <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>3.6</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>4.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.11</v>
+        <v>1.96</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AM5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BD6" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="BE6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF6" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="S7" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>4.4</v>
+        <v>4.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
         <v>1.35</v>
@@ -1825,40 +1825,40 @@
         <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AE7" t="n">
         <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AI7" t="n">
         <v>8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AL7" t="n">
         <v>1.79</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,16 +1900,16 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
         <v>2.27</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF7" t="n">
         <v>1.13</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,80 +2180,80 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>3.13</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.92</v>
+        <v>1.95</v>
       </c>
       <c r="T9" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>3.98</v>
+        <v>7.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="X9" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AD9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN9" t="n">
         <v>2.65</v>
       </c>
-      <c r="AE9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>6.66</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>7.09</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="AA10" t="n">
         <v>1.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,113 +2574,113 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U11" t="n">
         <v>3.25</v>
       </c>
-      <c r="R11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2.1</v>
       </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW11" t="n">
         <v>1.38</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AX11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.05</v>
       </c>
-      <c r="AK11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,37 +2771,37 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>4.33</v>
+        <v>4.86</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="X12" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.11</v>
@@ -2813,10 +2813,10 @@
         <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>2.2</v>
@@ -2828,7 +2828,7 @@
         <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.18</v>
@@ -2840,10 +2840,10 @@
         <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>4.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL13" t="n">
         <v>1.85</v>
       </c>
-      <c r="U13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AM13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
         <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>4.93</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="X14" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>1.34</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR14" t="n">
         <v>2.41</v>
@@ -3279,20 +3279,20 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.22</v>
       </c>
-      <c r="BC14" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46149.5625</v>
+        <v>46149.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BA15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="BB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>5.9</v>
+        <v>5.05</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.49</v>
+        <v>3.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.88</v>
+        <v>6.37</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.47</v>
+        <v>1.95</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU17" t="n">
         <v>2.88</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.68</v>
-      </c>
       <c r="AV17" t="n">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R18" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="S18" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="X18" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY18" t="n">
+      <c r="BC18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="R20" t="n">
-        <v>6.5</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>6.15</v>
       </c>
       <c r="T20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE20" t="n">
         <v>2.15</v>
       </c>
-      <c r="U20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="BF20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z21" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="AA21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="BC21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AL21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BF21" t="n">
         <v>1.13</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,85 +4741,85 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AD22" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.15</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22" t="n">
         <v>2.21</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4941,25 +4941,25 @@
         <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="V23" t="n">
         <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="X23" t="n">
         <v>3.08</v>
@@ -4974,25 +4974,25 @@
         <v>1.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AD23" t="n">
         <v>2.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" t="n">
         <v>7.5</v>
@@ -5016,34 +5016,34 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-05-07.xlsx
+++ b/jogos_2026-05-07.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD2" t="n">
         <v>3.6</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS3" t="n">
         <v>3.1</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AT3" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.05</v>
+        <v>3.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>9.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.33</v>
       </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AD6" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AM6" t="n">
         <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" t="n">
         <v>3.8</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.34</v>
-      </c>
       <c r="BE7" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AG8" t="n">
         <v>3.5</v>
       </c>
-      <c r="R8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AH8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL8" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,112 +2180,112 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>9.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.95</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>7.65</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="X9" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AF9" t="n">
         <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AH9" t="n">
         <v>1.22</v>
       </c>
       <c r="AI9" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
         <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.65</v>
+        <v>1.05</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2294,16 +2294,16 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="BF9" t="n">
         <v>1.14</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>4.86</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="T11" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.11</v>
+        <v>3.32</v>
       </c>
       <c r="X11" t="n">
-        <v>3.7</v>
+        <v>2.29</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>1.36</v>
       </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>4.86</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>3.32</v>
+        <v>2.67</v>
       </c>
       <c r="X12" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,113 +2968,113 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U13" t="n">
         <v>3.25</v>
       </c>
-      <c r="R13" t="n">
-        <v>4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK13" t="n">
         <v>2.1</v>
       </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="AL13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW13" t="n">
         <v>1.38</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AX13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.05</v>
       </c>
-      <c r="AK13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.75</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="X15" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.11</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.18</v>
+        <v>4.65</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="BC18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BE18" t="n">
         <v>1.45</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z20" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA20" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.08</v>
+        <v>2.6</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.13</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.94</v>
+        <v>5.75</v>
       </c>
       <c r="R21" t="n">
-        <v>7.9</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>1.81</v>
+        <v>6.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.59</v>
+        <v>4.1</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI21" t="n">
         <v>3</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AJ21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
         <v>1.99</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE21" t="n">
         <v>2.15</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1